--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -29,17 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -60,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,25 +436,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Mov</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Participante</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Signo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Exactos</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Totales</t>
         </is>
@@ -472,19 +471,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Jorge_Gamero</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
         <v>34</v>
       </c>
     </row>
@@ -494,19 +498,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Álvaro_Extremera</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>32</v>
       </c>
     </row>
@@ -516,19 +525,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Noel_Olivares</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>6</v>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
         <v>30</v>
       </c>
     </row>
@@ -538,19 +552,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Nessi_Morant</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>29</v>
       </c>
     </row>
@@ -560,19 +579,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>David_Cabesa</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
         <v>28</v>
       </c>
     </row>
@@ -582,19 +606,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>28</v>
       </c>
     </row>
@@ -604,19 +633,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Ángel_Gutiérrez</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
         <v>28</v>
       </c>
     </row>
@@ -626,19 +660,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
         <v>26</v>
       </c>
     </row>
@@ -648,19 +687,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>6</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>3</v>
+      <c r="E10" t="n">
+        <v>1</v>
       </c>
       <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
         <v>24</v>
       </c>
     </row>
@@ -670,19 +714,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Alberto_Villardón</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>5</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>3</v>
+      <c r="E11" t="n">
+        <v>1</v>
       </c>
       <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -692,19 +741,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Alvaro_Terron</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>3</v>
+      <c r="E12" t="n">
+        <v>1</v>
       </c>
       <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
         <v>22</v>
       </c>
     </row>
@@ -714,19 +768,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Raúl_Canabal</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>3</v>
+      <c r="E13" t="n">
+        <v>1</v>
       </c>
       <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
         <v>22</v>
       </c>
     </row>
@@ -736,19 +795,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>21</v>
       </c>
     </row>
@@ -758,19 +822,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>David_De_Paz</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>6</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
         <v>21</v>
       </c>
     </row>
@@ -780,19 +849,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Carlos_Moreno</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>6</v>
       </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1</v>
+      <c r="E16" t="n">
+        <v>3</v>
       </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
         <v>20</v>
       </c>
     </row>
@@ -802,19 +876,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Javier_García</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>6</v>
       </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1</v>
+      <c r="E17" t="n">
+        <v>3</v>
       </c>
       <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>20</v>
       </c>
     </row>
@@ -824,19 +903,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Javier_Leton</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>6</v>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>19</v>
       </c>
     </row>
@@ -846,19 +930,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Alberto_Gay</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>18</v>
       </c>
     </row>
@@ -868,19 +957,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>18</v>
       </c>
     </row>
@@ -890,19 +984,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Alejandro_Sánchez</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>6</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
         <v>17</v>
       </c>
     </row>
@@ -912,19 +1011,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Sergio_Fernandez</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>4</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
         <v>15</v>
       </c>
     </row>
@@ -934,19 +1038,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>7</v>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
         <v>15</v>
       </c>
     </row>
@@ -956,19 +1065,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Ruth_Galvin</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
         <v>15</v>
       </c>
     </row>
@@ -978,19 +1092,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>6</v>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1000,19 +1119,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Cristian_Luque</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1022,19 +1146,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Óscar_Espinosa</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>6</v>
       </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1044,19 +1173,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Jesús_García</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>6</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="F28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>6</v>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
         <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>32</v>
@@ -525,25 +525,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -552,25 +552,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -591,13 +591,13 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -606,25 +606,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -633,16 +633,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -651,7 +651,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -660,25 +660,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -687,25 +687,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -714,16 +714,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -732,7 +732,7 @@
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -741,25 +741,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -768,16 +768,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -786,7 +786,7 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -795,25 +795,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -822,25 +822,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -849,25 +849,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -876,25 +876,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -903,25 +903,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -930,25 +930,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -957,25 +957,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -984,25 +984,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>6</v>
       </c>
       <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -1029,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1038,25 +1038,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -1065,19 +1065,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -1110,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1137,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -498,25 +498,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -525,25 +525,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -552,25 +552,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -579,25 +579,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -606,25 +606,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -687,19 +687,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -714,25 +714,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -741,16 +741,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -768,25 +768,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -795,25 +795,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -840,7 +840,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -867,7 +867,7 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
@@ -948,7 +948,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -957,22 +957,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>20</v>
@@ -984,25 +984,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1011,16 +1011,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -1029,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1038,16 +1038,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -1056,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1065,25 +1065,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -1092,25 +1092,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>↑3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>↑3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -471,25 +471,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -498,25 +498,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
       <c r="G3" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -525,25 +525,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -552,25 +552,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
         <v>5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -579,25 +579,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -606,25 +606,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
       <c r="G7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -633,25 +633,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
       <c r="G8" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -660,25 +660,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -687,12 +687,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -702,10 +702,10 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -714,25 +714,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -741,25 +741,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -768,25 +768,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
       <c r="G13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -795,25 +795,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -822,25 +822,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -849,25 +849,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -876,25 +876,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -903,25 +903,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -942,13 +942,13 @@
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -957,25 +957,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -984,25 +984,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1011,25 +1011,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -1056,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1065,16 +1065,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -1110,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1161,10 +1161,10 @@
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -480,16 +480,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -503,20 +503,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -530,20 +530,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -579,25 +579,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>↑4</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -606,7 +606,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -633,7 +633,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -660,16 +660,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>↓4</t>
+          <t>↑4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -678,7 +678,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -692,20 +692,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -714,16 +714,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>↑3</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -732,7 +732,7 @@
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -741,7 +741,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -759,7 +759,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -768,25 +768,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>↑3</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
       <c r="G13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -795,7 +795,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -813,7 +813,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -822,16 +822,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>↑6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -840,7 +840,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -849,25 +849,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>↑4</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -876,7 +876,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>↑4</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>5</v>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -903,25 +903,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
       <c r="G18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -930,25 +930,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -957,25 +957,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>↓5</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -984,25 +984,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -1011,25 +1011,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -1056,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -1110,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,16 +480,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -507,16 +507,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -579,7 +579,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -606,25 +606,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -633,22 +633,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>36</v>
@@ -660,25 +660,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>↑4</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -687,7 +687,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -705,7 +705,7 @@
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -714,25 +714,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>↑3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -741,25 +741,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -773,11 +773,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -786,7 +786,7 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -795,25 +795,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -822,25 +822,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>↑6</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -849,25 +849,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -876,25 +876,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -903,7 +903,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -921,7 +921,7 @@
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -930,7 +930,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
@@ -948,7 +948,7 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -957,25 +957,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -984,7 +984,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -1002,7 +1002,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -1038,16 +1038,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -1056,7 +1056,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -1065,25 +1065,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1092,25 +1092,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1164,7 +1164,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
@@ -489,7 +489,7 @@
         <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -498,25 +498,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -525,25 +525,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -606,25 +606,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>↑4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -633,25 +633,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -660,25 +660,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>↑3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -687,25 +687,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -714,25 +714,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>↑3</t>
+          <t>↑4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
         <v>7</v>
       </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -741,25 +741,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>↑3</t>
+          <t>↓4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -768,25 +768,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>↓4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -795,25 +795,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>↑6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -822,25 +822,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>↓5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -849,25 +849,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -881,20 +881,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -903,25 +903,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↑4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -930,25 +930,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
         <v>3</v>
       </c>
-      <c r="F19" t="n">
-        <v>2</v>
-      </c>
       <c r="G19" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -957,25 +957,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>↑4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -984,25 +984,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
@@ -1011,25 +1011,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>↓3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -1038,25 +1038,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -1065,25 +1065,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>↑3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
       <c r="G24" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1146,25 +1146,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -1173,25 +1173,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
@@ -489,7 +489,7 @@
         <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>↑1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
@@ -543,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>6</v>
@@ -570,7 +570,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -597,7 +597,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -606,7 +606,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>↑4</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -633,7 +633,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>↑3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>↑4</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>↑4</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
@@ -732,7 +732,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -741,7 +741,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>↓4</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -768,7 +768,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>↓4</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -786,7 +786,7 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -795,7 +795,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>↑6</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -813,7 +813,7 @@
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -822,7 +822,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>↓5</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -840,7 +840,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -849,7 +849,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -867,7 +867,7 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -876,25 +876,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -903,22 +903,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>↑4</t>
+          <t>↑1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>33</v>
@@ -930,25 +930,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>↓2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -957,22 +957,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>↑4</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>32</v>
@@ -984,25 +984,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>↓4</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
@@ -1011,25 +1011,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>↓3</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
       <c r="G22" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>↓2</t>
+          <t>↑2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1065,25 +1065,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>↑3</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -1092,22 +1092,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>↓1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
         <v>30</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>↑2</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1137,7 +1137,7 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>↓1</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
@@ -1164,7 +1164,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>↓5</t>
+          <t>=</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,30 +436,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mov</t>
+          <t>Participante</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Participante</t>
+          <t>Signo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Signo</t>
+          <t>Diferencia</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Diferencia</t>
+          <t>Exactos</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Exactos</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Totales</t>
         </is>
@@ -471,24 +466,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>David_Cabesa</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -498,24 +488,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
           <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>13</v>
+      </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" t="n">
         <v>54</v>
       </c>
     </row>
@@ -525,24 +510,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>Noel_Olivares</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
         <v>51</v>
       </c>
     </row>
@@ -552,24 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
           <t>Jorge_Gamero</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
         <v>49</v>
       </c>
     </row>
@@ -579,24 +554,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>Nessi_Morant</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>11</v>
+      </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
         <v>45</v>
       </c>
     </row>
@@ -606,24 +576,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
           <t>Alberto_Villardón</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
         <v>45</v>
       </c>
     </row>
@@ -633,24 +598,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
           <t>Álvaro_Extremera</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
         <v>44</v>
       </c>
     </row>
@@ -660,24 +620,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
         <v>42</v>
       </c>
     </row>
@@ -687,24 +642,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
           <t>David_De_Paz</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="n">
         <v>41</v>
       </c>
     </row>
@@ -714,24 +664,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
           <t>Carlos_Moreno</t>
         </is>
       </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
         <v>41</v>
       </c>
     </row>
@@ -741,24 +686,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>13</v>
+      </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="n">
         <v>40</v>
       </c>
     </row>
@@ -768,24 +708,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
           <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
         <v>40</v>
       </c>
     </row>
@@ -795,24 +730,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>Alvaro_Terron</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="n">
         <v>39</v>
       </c>
     </row>
@@ -822,24 +752,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>Ángel_Gutiérrez</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
         <v>39</v>
       </c>
     </row>
@@ -849,24 +774,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
           <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>12</v>
+      </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
         <v>38</v>
       </c>
     </row>
@@ -876,24 +796,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>↑1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
           <t>Alejandro_Sánchez</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
         <v>34</v>
       </c>
     </row>
@@ -903,24 +818,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>↑1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
           <t>Alberto_Gay</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" t="n">
         <v>33</v>
       </c>
     </row>
@@ -930,24 +840,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>↓2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
           <t>Javier_García</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
         <v>33</v>
       </c>
     </row>
@@ -957,24 +862,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>↑2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
           <t>Javier_Leton</t>
         </is>
       </c>
+      <c r="C20" t="n">
+        <v>13</v>
+      </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="n">
         <v>32</v>
       </c>
     </row>
@@ -984,24 +884,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>↓1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>Sergio_Fernandez</t>
         </is>
       </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1011,24 +906,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>↓1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>Raúl_Canabal</t>
         </is>
       </c>
+      <c r="C22" t="n">
+        <v>11</v>
+      </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1038,24 +928,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>↑2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
           <t>Óscar_Espinosa</t>
         </is>
       </c>
+      <c r="C23" t="n">
+        <v>11</v>
+      </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
         <v>31</v>
       </c>
     </row>
@@ -1065,24 +950,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>↓1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
           <t>Ruth_Galvin</t>
         </is>
       </c>
+      <c r="C24" t="n">
+        <v>11</v>
+      </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
         <v>31</v>
       </c>
     </row>
@@ -1092,24 +972,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>↓1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
           <t>Cristian_Luque</t>
         </is>
       </c>
+      <c r="C25" t="n">
+        <v>9</v>
+      </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1119,24 +994,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
           <t>Jesús_García</t>
         </is>
       </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1146,24 +1016,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
           <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
+      <c r="C27" t="n">
+        <v>13</v>
+      </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1173,24 +1038,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
+      <c r="C28" t="n">
+        <v>12</v>
+      </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
         <v>23</v>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -479,7 +479,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -545,7 +545,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
@@ -752,11 +752,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -765,7 +765,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -787,7 +787,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
@@ -897,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
@@ -950,17 +950,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
         <v>31</v>
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -1038,11 +1038,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
@@ -1051,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,11 @@
           <t>Totales</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evolución</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -481,6 +486,11 @@
       <c r="F2" t="n">
         <v>61</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -502,6 +512,11 @@
       </c>
       <c r="F3" t="n">
         <v>57</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -525,6 +540,11 @@
       <c r="F4" t="n">
         <v>54</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +567,11 @@
       <c r="F5" t="n">
         <v>50</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +594,11 @@
       <c r="F6" t="n">
         <v>47</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +621,11 @@
       <c r="F7" t="n">
         <v>46</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +648,11 @@
       <c r="F8" t="n">
         <v>46</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +675,11 @@
       <c r="F9" t="n">
         <v>46</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +702,11 @@
       <c r="F10" t="n">
         <v>46</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +729,11 @@
       <c r="F11" t="n">
         <v>45</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +756,11 @@
       <c r="F12" t="n">
         <v>44</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +783,11 @@
       <c r="F13" t="n">
         <v>44</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +810,11 @@
       <c r="F14" t="n">
         <v>41</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +837,11 @@
       <c r="F15" t="n">
         <v>41</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +864,11 @@
       <c r="F16" t="n">
         <v>39</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +891,11 @@
       <c r="F17" t="n">
         <v>38</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +918,11 @@
       <c r="F18" t="n">
         <v>35</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +945,11 @@
       <c r="F19" t="n">
         <v>34</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +972,11 @@
       <c r="F20" t="n">
         <v>34</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +999,11 @@
       <c r="F21" t="n">
         <v>33</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +1026,11 @@
       <c r="F22" t="n">
         <v>33</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1053,11 @@
       <c r="F23" t="n">
         <v>33</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1080,11 @@
       <c r="F24" t="n">
         <v>31</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1107,11 @@
       <c r="F25" t="n">
         <v>31</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1134,11 @@
       <c r="F26" t="n">
         <v>28</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1161,11 @@
       <c r="F27" t="n">
         <v>27</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1052,6 +1187,11 @@
       </c>
       <c r="F28" t="n">
         <v>24</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>🆕</t>
+          <t>➡️</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➡️</t>
+          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#cccccc'&gt;➡️ 0&lt;/span&gt;</t>
+          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#bdc3c7'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -511,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -538,7 +538,7 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -565,7 +565,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -592,7 +592,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -619,7 +619,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -633,20 +633,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -673,7 +673,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -687,17 +687,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
         <v>46</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -727,7 +727,7 @@
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -754,7 +754,7 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
@@ -781,7 +781,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -808,7 +808,7 @@
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -835,7 +835,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -889,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
@@ -916,7 +916,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
@@ -943,7 +943,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
@@ -970,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
@@ -997,7 +997,7 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
@@ -1024,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1051,7 +1051,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
@@ -1078,7 +1078,7 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
         <v>2</v>
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1159,7 +1159,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
@@ -1186,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -511,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -538,7 +538,7 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -552,20 +552,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -579,20 +579,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -633,20 +633,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -673,7 +673,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -700,7 +700,7 @@
         <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -714,11 +714,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -727,7 +727,7 @@
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -741,20 +741,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
@@ -781,7 +781,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -795,20 +795,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -835,7 +835,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -889,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
@@ -916,7 +916,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
@@ -943,7 +943,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
@@ -970,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
@@ -997,7 +997,7 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
@@ -1024,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1051,7 +1051,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
@@ -1078,7 +1078,7 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
         <v>5</v>
@@ -1105,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
         <v>2</v>
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1159,7 +1159,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
@@ -1186,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -481,10 +481,10 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -511,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -538,7 +538,7 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -559,13 +559,13 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,24 +606,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -633,24 +633,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,24 +660,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -687,24 +687,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
-        <v>5</v>
-      </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -714,11 +714,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -727,11 +727,11 @@
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -741,24 +741,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -768,24 +768,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -835,7 +835,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -856,13 +856,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -876,24 +876,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -903,24 +903,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -957,24 +957,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -997,11 +997,11 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1011,24 +1011,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1038,24 +1038,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1065,20 +1065,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1092,24 +1092,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1132,11 +1132,11 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1153,13 +1153,13 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -481,10 +481,10 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -511,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -525,24 +525,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -552,24 +552,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,13 +586,13 @@
         <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -606,24 +606,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -633,20 +633,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -660,24 +660,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -687,24 +687,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>14</v>
       </c>
       <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -714,20 +714,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -741,20 +741,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
-        <v>5</v>
-      </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -768,11 +768,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
@@ -781,7 +781,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -808,7 +808,7 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -822,24 +822,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -876,11 +876,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
@@ -889,11 +889,11 @@
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -903,20 +903,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -930,24 +930,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -957,24 +957,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -997,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1011,24 +1011,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1038,24 +1038,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1065,24 +1065,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1092,24 +1092,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
         <v>2</v>
       </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1183,10 +1183,10 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -505,13 +505,13 @@
         <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -525,20 +525,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -552,20 +552,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -579,24 +579,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -606,24 +606,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -633,24 +633,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,24 +660,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -687,24 +687,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -741,20 +741,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -778,14 +778,14 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -795,24 +795,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -822,24 +822,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -849,24 +849,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -883,17 +883,17 @@
         <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -903,24 +903,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -957,11 +957,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
@@ -970,11 +970,11 @@
         <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -984,24 +984,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1011,24 +1011,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1038,24 +1038,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1065,24 +1065,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1092,24 +1092,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1177,16 +1177,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,10 +456,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Extras</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Totales</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Evolución</t>
         </is>
@@ -471,24 +476,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>82</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+        <v>105</v>
+      </c>
+      <c r="G2" t="n">
+        <v>175</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -498,24 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>69</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+        <v>81</v>
+      </c>
+      <c r="G3" t="n">
+        <v>164</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -525,24 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+        <v>90</v>
+      </c>
+      <c r="G4" t="n">
+        <v>160</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -565,11 +579,14 @@
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>64</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+        <v>93</v>
+      </c>
+      <c r="G5" t="n">
+        <v>158</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -583,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -592,11 +609,14 @@
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
+        <v>93</v>
+      </c>
+      <c r="G6" t="n">
+        <v>157</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -606,24 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+        <v>99</v>
+      </c>
+      <c r="G7" t="n">
+        <v>156</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -633,24 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+        <v>90</v>
+      </c>
+      <c r="G8" t="n">
+        <v>148</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,24 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+        <v>96</v>
+      </c>
+      <c r="G9" t="n">
+        <v>147</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -687,24 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+        <v>96</v>
+      </c>
+      <c r="G10" t="n">
+        <v>144</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -714,24 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+        <v>84</v>
+      </c>
+      <c r="G11" t="n">
+        <v>144</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -741,24 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+        <v>84</v>
+      </c>
+      <c r="G12" t="n">
+        <v>143</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -768,24 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+        <v>93</v>
+      </c>
+      <c r="G13" t="n">
+        <v>141</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -795,24 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
+        <v>75</v>
+      </c>
+      <c r="G14" t="n">
+        <v>140</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -822,24 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+        <v>81</v>
+      </c>
+      <c r="G15" t="n">
+        <v>137</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -849,24 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+        <v>81</v>
+      </c>
+      <c r="G16" t="n">
+        <v>135</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -876,24 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+        <v>78</v>
+      </c>
+      <c r="G17" t="n">
+        <v>135</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -903,24 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
       <c r="F18" t="n">
-        <v>47</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+        <v>81</v>
+      </c>
+      <c r="G18" t="n">
+        <v>131</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,24 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
+        <v>84</v>
+      </c>
+      <c r="G19" t="n">
+        <v>130</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -957,11 +1016,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
@@ -970,11 +1029,14 @@
         <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+        <v>84</v>
+      </c>
+      <c r="G20" t="n">
+        <v>129</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -984,24 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+        <v>81</v>
+      </c>
+      <c r="G21" t="n">
+        <v>126</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1011,24 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+        <v>81</v>
+      </c>
+      <c r="G22" t="n">
+        <v>124</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1038,24 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+        <v>66</v>
+      </c>
+      <c r="G23" t="n">
+        <v>123</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -8&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1065,11 +1136,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
@@ -1078,11 +1149,14 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+        <v>75</v>
+      </c>
+      <c r="G24" t="n">
+        <v>122</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
@@ -1105,11 +1179,14 @@
         <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+        <v>72</v>
+      </c>
+      <c r="G25" t="n">
+        <v>116</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+        <v>69</v>
+      </c>
+      <c r="G26" t="n">
+        <v>116</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
+        <v>60</v>
+      </c>
+      <c r="G27" t="n">
+        <v>97</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1173,24 +1256,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>17</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>36</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+        <v>57</v>
+      </c>
+      <c r="G28" t="n">
+        <v>97</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -476,27 +476,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -579,10 +579,10 @@
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>158</v>
+        <v>65</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +8&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +12&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -7&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -879,14 +879,14 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -9&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,11 +1016,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
@@ -1029,14 +1029,14 @@
         <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,11 +1046,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1059,10 +1059,10 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -8&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,11 +1136,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
@@ -1149,14 +1149,14 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1179,10 +1179,10 @@
         <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,23 +1226,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1256,23 +1256,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +8&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +12&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -7&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -9&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +6&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -746,17 +746,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,11 +866,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -882,11 +882,11 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -492,7 +492,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,11 +686,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -702,11 +702,11 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -746,14 +746,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
@@ -762,11 +762,11 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,14 +776,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -792,11 +792,11 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
         <v>7</v>
       </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,23 +866,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1016,14 +1016,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
@@ -1032,11 +1032,11 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,11 +1106,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
         <v>3</v>
@@ -1122,11 +1122,11 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,14 +1166,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>18</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>4</v>
@@ -1182,11 +1182,11 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1260,19 +1260,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -492,7 +492,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>6</v>
@@ -522,11 +522,11 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
@@ -552,11 +552,11 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -630,23 +630,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,23 +660,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,14 +686,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -702,11 +702,11 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,14 +716,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
@@ -732,11 +732,11 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>6</v>
@@ -852,11 +852,11 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
@@ -882,11 +882,11 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
         <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>5</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="n">
-        <v>6</v>
-      </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
@@ -1032,11 +1032,11 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1062,11 +1062,11 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="n">
-        <v>4</v>
-      </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
         <v>19</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -1152,11 +1152,11 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
         <v>3</v>
       </c>
-      <c r="E25" t="n">
-        <v>4</v>
-      </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1212,11 +1212,11 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1256,27 +1256,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -7&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -7&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
@@ -492,7 +492,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,23 +510,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
@@ -552,11 +552,11 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -612,11 +612,11 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
@@ -672,11 +672,11 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,23 +716,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -786,17 +786,17 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,14 +806,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>6</v>
@@ -822,11 +822,11 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -882,11 +882,11 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>6</v>
@@ -942,11 +942,11 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,14 +956,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
@@ -972,11 +972,11 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,23 +986,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1016,14 +1016,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,14 +1076,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
@@ -1092,11 +1092,11 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,11 +1166,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,11 +1182,11 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
@@ -1242,11 +1242,11 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1256,27 +1256,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +6&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -483,7 +483,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
@@ -492,7 +492,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>7</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
         <v>7</v>
       </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
         <v>9</v>
       </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -726,13 +726,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -756,13 +756,13 @@
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>4</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1016,11 +1016,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
@@ -1032,11 +1032,11 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
         <v>6</v>
       </c>
-      <c r="E22" t="n">
-        <v>4</v>
-      </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,14 +1136,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -1152,11 +1152,11 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1206,13 +1206,13 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>23</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -513,16 +513,16 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,14 +656,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>9</v>
@@ -672,11 +672,11 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
         <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>6</v>
@@ -852,11 +852,11 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,14 +926,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>6</v>
@@ -942,11 +942,11 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,14 +956,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
@@ -972,11 +972,11 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,14 +986,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>4</v>
@@ -1002,11 +1002,11 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,14 +1136,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -1152,11 +1152,11 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,14 +1166,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
         <v>4</v>
@@ -1182,11 +1182,11 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1256,11 +1256,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D28" t="n">
         <v>5</v>
@@ -1272,11 +1272,11 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -492,7 +492,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -552,11 +552,11 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -582,11 +582,11 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -612,11 +612,11 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -642,11 +642,11 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -672,11 +672,11 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -702,11 +702,11 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -732,11 +732,11 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -762,11 +762,11 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
@@ -792,11 +792,11 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -822,11 +822,11 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,7 +852,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -882,11 +882,11 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,23 +896,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -972,11 +972,11 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -1002,11 +1002,11 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1032,11 +1032,11 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1062,11 +1062,11 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" t="n">
         <v>8</v>
@@ -1092,11 +1092,11 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
@@ -1122,11 +1122,11 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
         <v>7</v>
@@ -1152,11 +1152,11 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D25" t="n">
         <v>8</v>
@@ -1182,11 +1182,11 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1212,11 +1212,11 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>6</v>
@@ -1242,11 +1242,11 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D28" t="n">
         <v>5</v>
@@ -1272,11 +1272,11 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -476,27 +476,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>22</v>
       </c>
       <c r="D2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="n">
-        <v>11</v>
-      </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -546,17 +546,17 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,14 +566,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>11</v>
@@ -582,11 +582,11 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,11 +626,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -642,11 +642,11 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,19 +750,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
         <v>9</v>
       </c>
-      <c r="E13" t="n">
-        <v>6</v>
-      </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,14 +836,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>6</v>
@@ -852,11 +852,11 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,14 +896,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>6</v>
@@ -912,11 +912,11 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,23 +926,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
         <v>6</v>
       </c>
-      <c r="E17" t="n">
-        <v>7</v>
-      </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +8&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,14 +1016,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>5</v>
@@ -1032,11 +1032,11 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
@@ -1092,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
         <v>6</v>
@@ -1122,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1136,14 +1136,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -1152,11 +1152,11 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,14 +1166,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
         <v>4</v>
@@ -1182,11 +1182,11 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1226,14 +1226,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
@@ -1242,11 +1242,11 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -1272,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -476,27 +476,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -510,23 +510,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,23 +536,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="E4" t="n">
-        <v>11</v>
-      </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
         <v>11</v>
       </c>
-      <c r="E8" t="n">
-        <v>8</v>
-      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
         <v>7</v>
       </c>
-      <c r="E12" t="n">
-        <v>9</v>
-      </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,23 +806,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -836,23 +836,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>25</v>
       </c>
       <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
         <v>9</v>
       </c>
-      <c r="E14" t="n">
-        <v>6</v>
-      </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,14 +926,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>6</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -972,11 +972,11 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,14 +986,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
@@ -1002,11 +1002,11 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +8&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
@@ -1032,11 +1032,11 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,11 +1136,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
         <v>9</v>
@@ -1152,11 +1152,11 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,14 +1226,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1266,13 +1266,13 @@
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>12</v>
@@ -492,11 +492,11 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,23 +626,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>11</v>
@@ -672,11 +672,11 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="n">
-        <v>8</v>
-      </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>9</v>
@@ -852,11 +852,11 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,14 +866,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>7</v>
@@ -882,11 +882,11 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,14 +896,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
@@ -912,11 +912,11 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>6</v>
@@ -942,11 +942,11 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
@@ -1002,11 +1002,11 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,14 +1076,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>7</v>
@@ -1092,11 +1092,11 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,14 +1196,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
         <v>5</v>
@@ -1212,11 +1212,11 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1256,14 +1256,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
@@ -1272,11 +1272,11 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -476,27 +476,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>113</v>
+        <v>214</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G3" t="n">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>109</v>
+        <v>203</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +6&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>104</v>
+        <v>192</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
         <v>9</v>
       </c>
-      <c r="E9" t="n">
-        <v>11</v>
-      </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G9" t="n">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" t="n">
         <v>7</v>
       </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,23 +896,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="n">
-        <v>6</v>
-      </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G20" t="n">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G21" t="n">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G22" t="n">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G23" t="n">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Miguel_Lara_Cantón</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>27</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
         <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G24" t="n">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G25" t="n">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G26" t="n">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1256,27 +1256,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Miguel_Lara_Cantón</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +7&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -6&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -612,7 +612,7 @@
         <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G7" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G13" t="n">
         <v>183</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G16" t="n">
         <v>178</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
         <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G21" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
         <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -486,13 +486,13 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -516,17 +516,17 @@
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -546,13 +546,13 @@
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -576,17 +576,17 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -612,7 +612,7 @@
         <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -642,11 +642,11 @@
         <v>99</v>
       </c>
       <c r="G7" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -672,11 +672,11 @@
         <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -732,11 +732,11 @@
         <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
         <v>13</v>
       </c>
-      <c r="E12" t="n">
-        <v>7</v>
-      </c>
       <c r="F12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -822,11 +822,11 @@
         <v>96</v>
       </c>
       <c r="G13" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
@@ -852,11 +852,11 @@
         <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
@@ -882,11 +882,11 @@
         <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -912,11 +912,11 @@
         <v>99</v>
       </c>
       <c r="G16" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -1002,11 +1002,11 @@
         <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
@@ -1032,11 +1032,11 @@
         <v>78</v>
       </c>
       <c r="G20" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G22" t="n">
         <v>170</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
         <v>12</v>
@@ -1152,11 +1152,11 @@
         <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,11 +1182,11 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
@@ -1212,11 +1212,11 @@
         <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1242,11 +1242,11 @@
         <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>26</v>
       </c>
       <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
         <v>13</v>
       </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
         <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
@@ -852,11 +852,11 @@
         <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,23 +866,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G16" t="n">
         <v>183</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
         <v>7</v>
       </c>
-      <c r="E17" t="n">
-        <v>10</v>
-      </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G17" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" t="n">
         <v>8</v>
       </c>
-      <c r="E18" t="n">
-        <v>7</v>
-      </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
@@ -1032,11 +1032,11 @@
         <v>78</v>
       </c>
       <c r="G20" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>29</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G23" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G24" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>28</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G25" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
         <v>193</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
         <v>7</v>
       </c>
-      <c r="E16" t="n">
-        <v>10</v>
-      </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
         <v>183</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1026,17 +1026,17 @@
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
         <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G23" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>28</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G27" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G13" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
@@ -852,7 +852,7 @@
         <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G16" t="n">
         <v>183</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1086,17 +1086,17 @@
         <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G24" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
         <v>7</v>
       </c>
-      <c r="E26" t="n">
-        <v>4</v>
-      </c>
       <c r="F26" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G26" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G27" t="n">
         <v>165</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>26</v>
       </c>
       <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
         <v>13</v>
       </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
@@ -852,7 +852,7 @@
         <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
         <v>183</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1086,17 +1086,17 @@
         <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,7 +522,7 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -612,7 +612,7 @@
         <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -636,17 +636,17 @@
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G11" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -822,7 +822,7 @@
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G16" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G17" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -972,7 +972,7 @@
         <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" t="n">
         <v>9</v>
@@ -1092,7 +1092,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" t="n">
         <v>11</v>
@@ -1122,7 +1122,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" t="n">
         <v>8</v>
@@ -1152,7 +1152,7 @@
         <v>87</v>
       </c>
       <c r="G24" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -486,13 +486,13 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,11 +522,11 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
         <v>212</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G7" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -672,11 +672,11 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>13</v>
-      </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G10" t="n">
         <v>200</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,23 +806,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
         <v>11</v>
       </c>
-      <c r="E14" t="n">
-        <v>7</v>
-      </c>
       <c r="F14" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,20 +866,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
         <v>193</v>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
         <v>193</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,23 +926,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G18" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,23 +986,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
@@ -1032,11 +1032,11 @@
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G22" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G23" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,7 +522,7 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -606,17 +606,17 @@
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
         <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -642,11 +642,11 @@
         <v>93</v>
       </c>
       <c r="G7" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -672,7 +672,7 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -702,11 +702,11 @@
         <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,23 +746,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
         <v>9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>11</v>
       </c>
       <c r="F14" t="n">
         <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,23 +866,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G16" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" t="n">
         <v>7</v>
       </c>
-      <c r="E17" t="n">
-        <v>10</v>
-      </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
@@ -972,11 +972,11 @@
         <v>90</v>
       </c>
       <c r="G18" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -1002,11 +1002,11 @@
         <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
@@ -1032,7 +1032,7 @@
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,23 +1076,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
@@ -1152,11 +1152,11 @@
         <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
@@ -1212,7 +1212,7 @@
         <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
         <v>12</v>
@@ -1242,7 +1242,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D28" t="n">
         <v>8</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,11 +522,11 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -582,11 +582,11 @@
         <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -612,11 +612,11 @@
         <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -642,11 +642,11 @@
         <v>93</v>
       </c>
       <c r="G7" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -672,11 +672,11 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -702,11 +702,11 @@
         <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -732,11 +732,11 @@
         <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -762,11 +762,11 @@
         <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
@@ -792,11 +792,11 @@
         <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -822,11 +822,11 @@
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
@@ -852,7 +852,7 @@
         <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -882,11 +882,11 @@
         <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -912,11 +912,11 @@
         <v>99</v>
       </c>
       <c r="G16" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
@@ -942,11 +942,11 @@
         <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
@@ -972,11 +972,11 @@
         <v>90</v>
       </c>
       <c r="G18" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -1002,11 +1002,11 @@
         <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
@@ -1032,11 +1032,11 @@
         <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1062,11 +1062,11 @@
         <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" t="n">
         <v>8</v>
@@ -1092,11 +1092,11 @@
         <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
@@ -1122,11 +1122,11 @@
         <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1152,11 +1152,11 @@
         <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,11 +1182,11 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
@@ -1212,11 +1212,11 @@
         <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D27" t="n">
         <v>12</v>
@@ -1242,11 +1242,11 @@
         <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D28" t="n">
         <v>8</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,7 +522,7 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -582,7 +582,7 @@
         <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -672,7 +672,7 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
@@ -792,7 +792,7 @@
         <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
         <v>9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>11</v>
       </c>
       <c r="F13" t="n">
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G14" t="n">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -882,7 +882,7 @@
         <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -912,7 +912,7 @@
         <v>99</v>
       </c>
       <c r="G16" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G17" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G18" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1062,7 +1062,7 @@
         <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G23" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1152,7 +1152,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
@@ -1212,7 +1212,7 @@
         <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D27" t="n">
         <v>12</v>
@@ -1242,7 +1242,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D28" t="n">
         <v>8</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,11 +522,11 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G13" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,11 +522,11 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -582,11 +582,11 @@
         <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -612,7 +612,7 @@
         <v>93</v>
       </c>
       <c r="G6" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>14</v>
@@ -642,7 +642,7 @@
         <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -672,11 +672,11 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -776,23 +776,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -806,23 +806,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
@@ -852,7 +852,7 @@
         <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G15" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G17" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="n">
         <v>6</v>
       </c>
-      <c r="E19" t="n">
-        <v>5</v>
-      </c>
       <c r="F19" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1032,11 +1032,11 @@
         <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1062,11 +1062,11 @@
         <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G23" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1152,11 +1152,11 @@
         <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,11 +1182,11 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
@@ -1212,11 +1212,11 @@
         <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D27" t="n">
         <v>12</v>
@@ -1242,11 +1242,11 @@
         <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D28" t="n">
         <v>8</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +4&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,7 +522,7 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G10" t="n">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -792,7 +792,7 @@
         <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G13" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G14" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -912,7 +912,7 @@
         <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
@@ -942,7 +942,7 @@
         <v>99</v>
       </c>
       <c r="G17" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -972,7 +972,7 @@
         <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -1002,7 +1002,7 @@
         <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1032,7 +1032,7 @@
         <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1062,7 +1062,7 @@
         <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G23" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1152,7 +1152,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
@@ -1212,7 +1212,7 @@
         <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
@@ -1242,7 +1242,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
         <v>5</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,7 +522,7 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G4" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
         <v>9</v>
       </c>
-      <c r="E11" t="n">
-        <v>12</v>
-      </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G16" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
         <v>228</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G18" t="n">
         <v>228</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G23" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G24" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
@@ -1212,7 +1212,7 @@
         <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,23 +656,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G11" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,23 +806,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G14" t="n">
         <v>233</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,23 +1076,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G23" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -612,7 +612,7 @@
         <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -642,7 +642,7 @@
         <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
@@ -792,7 +792,7 @@
         <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -822,7 +822,7 @@
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
         <v>81</v>
       </c>
       <c r="G16" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
         <v>7</v>
       </c>
-      <c r="E17" t="n">
-        <v>10</v>
-      </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G17" t="n">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -1002,7 +1002,7 @@
         <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1032,7 +1032,7 @@
         <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1062,7 +1062,7 @@
         <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
         <v>8</v>
@@ -1122,7 +1122,7 @@
         <v>87</v>
       </c>
       <c r="G23" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>38</v>
       </c>
       <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
         <v>7</v>
       </c>
-      <c r="E26" t="n">
-        <v>4</v>
-      </c>
       <c r="F26" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G26" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,7 +522,7 @@
         <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -582,7 +582,7 @@
         <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
@@ -792,7 +792,7 @@
         <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -822,7 +822,7 @@
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,7 +852,7 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
@@ -882,7 +882,7 @@
         <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
         <v>7</v>
       </c>
-      <c r="E16" t="n">
-        <v>10</v>
-      </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G16" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G17" t="n">
         <v>238</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" t="n">
         <v>9</v>
       </c>
-      <c r="E19" t="n">
-        <v>6</v>
-      </c>
       <c r="F19" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G20" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1062,7 +1062,7 @@
         <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="n">
         <v>8</v>
@@ -1122,7 +1122,7 @@
         <v>87</v>
       </c>
       <c r="G23" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1152,7 +1152,7 @@
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,7 +522,7 @@
         <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
         <v>15</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -582,7 +582,7 @@
         <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -612,11 +612,11 @@
         <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -642,11 +642,11 @@
         <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -672,7 +672,7 @@
         <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
@@ -702,7 +702,7 @@
         <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -732,7 +732,7 @@
         <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
@@ -762,7 +762,7 @@
         <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
@@ -792,7 +792,7 @@
         <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -822,7 +822,7 @@
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,7 +852,7 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
@@ -882,7 +882,7 @@
         <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
@@ -912,11 +912,11 @@
         <v>96</v>
       </c>
       <c r="G16" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
@@ -942,11 +942,11 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -972,11 +972,11 @@
         <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
@@ -1002,11 +1002,11 @@
         <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" t="n">
         <v>9</v>
@@ -1032,11 +1032,11 @@
         <v>90</v>
       </c>
       <c r="G20" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G21" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1152,7 +1152,7 @@
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,11 +1182,11 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,23 +1196,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
-        <v>14</v>
-      </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +6&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
         <v>9</v>
       </c>
-      <c r="E13" t="n">
-        <v>12</v>
-      </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G13" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="G14" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
         <v>248</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
         <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G20" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -483,7 +483,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -522,11 +522,11 @@
         <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G4" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -612,7 +612,7 @@
         <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -642,7 +642,7 @@
         <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>8</v>
@@ -672,11 +672,11 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +6&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>14</v>
@@ -702,11 +702,11 @@
         <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
@@ -732,11 +732,11 @@
         <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -762,11 +762,11 @@
         <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -792,11 +792,11 @@
         <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -912,11 +912,11 @@
         <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -972,7 +972,7 @@
         <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
@@ -1002,7 +1002,7 @@
         <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
         <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G20" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,23 +1046,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>37</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G21" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -1092,11 +1092,11 @@
         <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         <v>41</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
         <v>5</v>
@@ -1122,7 +1122,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1152,7 +1152,7 @@
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
         <v>15</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
         <v>15</v>
@@ -582,11 +582,11 @@
         <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -612,7 +612,7 @@
         <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -642,7 +642,7 @@
         <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -672,7 +672,7 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
@@ -702,7 +702,7 @@
         <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -732,7 +732,7 @@
         <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -762,7 +762,7 @@
         <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -792,7 +792,7 @@
         <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -822,11 +822,11 @@
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,11 +852,11 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -882,11 +882,11 @@
         <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -912,7 +912,7 @@
         <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -972,7 +972,7 @@
         <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
@@ -1002,7 +1002,7 @@
         <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1016,23 +1016,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
         <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G20" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1046,23 +1046,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>37</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" t="n">
         <v>12</v>
@@ -1122,7 +1122,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1152,7 +1152,7 @@
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D26" t="n">
         <v>8</v>
@@ -1212,11 +1212,11 @@
         <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" t="n">
         <v>14</v>
@@ -1242,11 +1242,11 @@
         <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
         <v>15</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -522,11 +522,11 @@
         <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -552,11 +552,11 @@
         <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
         <v>15</v>
@@ -582,7 +582,7 @@
         <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -612,7 +612,7 @@
         <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -642,7 +642,7 @@
         <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -672,7 +672,7 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
@@ -702,7 +702,7 @@
         <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -732,7 +732,7 @@
         <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -762,7 +762,7 @@
         <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -792,7 +792,7 @@
         <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -822,7 +822,7 @@
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,7 +852,7 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -882,7 +882,7 @@
         <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -912,7 +912,7 @@
         <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G19" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1062,11 +1062,11 @@
         <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" t="n">
         <v>12</v>
@@ -1122,7 +1122,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
@@ -1152,7 +1152,7 @@
         <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1182,7 +1182,7 @@
         <v>81</v>
       </c>
       <c r="G25" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D26" t="n">
         <v>8</v>
@@ -1212,7 +1212,7 @@
         <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D27" t="n">
         <v>14</v>
@@ -1242,7 +1242,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
         <v>15</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -522,7 +522,7 @@
         <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
         <v>40</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>8</v>
@@ -672,7 +672,7 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -762,7 +762,7 @@
         <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -792,7 +792,7 @@
         <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -822,7 +822,7 @@
         <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,7 +852,7 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -882,7 +882,7 @@
         <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -912,7 +912,7 @@
         <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -972,11 +972,11 @@
         <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -1002,11 +1002,11 @@
         <v>87</v>
       </c>
       <c r="G19" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1032,11 +1032,11 @@
         <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
         <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G24" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alberto_Gay</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1226,27 +1226,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Alberto_Gay</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D28" t="n">
         <v>9</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G3" t="n">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G4" t="n">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -612,7 +612,7 @@
         <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
-        <v>15</v>
-      </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G7" t="n">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
         <v>9</v>
       </c>
-      <c r="E10" t="n">
-        <v>14</v>
-      </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -882,7 +882,7 @@
         <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -912,7 +912,7 @@
         <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
         <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1026,17 +1026,17 @@
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G20" t="n">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
         <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G22" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G23" t="n">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G24" t="n">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
         <v>4</v>
@@ -1182,7 +1182,7 @@
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
@@ -1212,7 +1212,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1242,7 +1242,7 @@
         <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
         <v>5</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -612,7 +612,7 @@
         <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -642,7 +642,7 @@
         <v>99</v>
       </c>
       <c r="G7" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -672,7 +672,7 @@
         <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
         <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
         <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -792,7 +792,7 @@
         <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -822,7 +822,7 @@
         <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,7 +852,7 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -972,7 +972,7 @@
         <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -1002,7 +1002,7 @@
         <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
         <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
@@ -1092,7 +1092,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" t="n">
         <v>12</v>
@@ -1152,7 +1152,7 @@
         <v>75</v>
       </c>
       <c r="G24" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
         <v>11</v>
@@ -1182,7 +1182,7 @@
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1242,7 +1242,7 @@
         <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G3" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G4" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -612,7 +612,7 @@
         <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -642,7 +642,7 @@
         <v>99</v>
       </c>
       <c r="G7" t="n">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -672,7 +672,7 @@
         <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -686,23 +686,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -716,23 +716,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -792,7 +792,7 @@
         <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -822,7 +822,7 @@
         <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,7 +852,7 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -866,23 +866,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -896,23 +896,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -972,7 +972,7 @@
         <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -1002,7 +1002,7 @@
         <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1062,7 +1062,7 @@
         <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
@@ -1092,7 +1092,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="n">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" t="n">
         <v>12</v>
@@ -1152,7 +1152,7 @@
         <v>75</v>
       </c>
       <c r="G24" t="n">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" t="n">
         <v>11</v>
@@ -1182,7 +1182,7 @@
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1242,7 +1242,7 @@
         <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
@@ -522,7 +522,7 @@
         <v>96</v>
       </c>
       <c r="G3" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -552,7 +552,7 @@
         <v>93</v>
       </c>
       <c r="G4" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
       <c r="F7" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -656,27 +656,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
-        <v>15</v>
-      </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -686,27 +686,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
         <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
         <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -792,7 +792,7 @@
         <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -822,7 +822,7 @@
         <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,7 +852,7 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -972,7 +972,7 @@
         <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -1002,7 +1002,7 @@
         <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1032,7 +1032,7 @@
         <v>87</v>
       </c>
       <c r="G20" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G21" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="n">
         <v>6</v>
       </c>
-      <c r="E22" t="n">
-        <v>7</v>
-      </c>
       <c r="F22" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G22" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" t="n">
         <v>12</v>
@@ -1152,7 +1152,7 @@
         <v>75</v>
       </c>
       <c r="G24" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
         <v>11</v>
@@ -1182,7 +1182,7 @@
         <v>96</v>
       </c>
       <c r="G25" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D26" t="n">
         <v>15</v>
@@ -1212,7 +1212,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1242,7 +1242,7 @@
         <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D28" t="n">
         <v>10</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
@@ -522,7 +522,7 @@
         <v>96</v>
       </c>
       <c r="G3" t="n">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -552,7 +552,7 @@
         <v>93</v>
       </c>
       <c r="G4" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -672,11 +672,11 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -702,11 +702,11 @@
         <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
@@ -732,11 +732,11 @@
         <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -792,7 +792,7 @@
         <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -822,7 +822,7 @@
         <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -852,7 +852,7 @@
         <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
@@ -882,11 +882,11 @@
         <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>14</v>
@@ -912,11 +912,11 @@
         <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -942,7 +942,7 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -972,7 +972,7 @@
         <v>81</v>
       </c>
       <c r="G18" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -1002,7 +1002,7 @@
         <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1032,7 +1032,7 @@
         <v>87</v>
       </c>
       <c r="G20" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -1062,11 +1062,11 @@
         <v>81</v>
       </c>
       <c r="G21" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -1092,11 +1092,11 @@
         <v>90</v>
       </c>
       <c r="G22" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G24" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
         <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G26" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D28" t="n">
         <v>10</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,20 +596,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G6" t="n">
         <v>320</v>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -672,7 +672,7 @@
         <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -702,7 +702,7 @@
         <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
@@ -732,7 +732,7 @@
         <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G12" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -822,7 +822,7 @@
         <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
@@ -882,7 +882,7 @@
         <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
         <v>14</v>
@@ -912,7 +912,7 @@
         <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -926,14 +926,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Álvaro_Extremera</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
@@ -942,11 +942,11 @@
         <v>81</v>
       </c>
       <c r="G17" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Alejandro_Sánchez</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -986,27 +986,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alejandro_Sánchez</t>
+          <t>Álvaro_Extremera</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1032,7 +1032,7 @@
         <v>87</v>
       </c>
       <c r="G20" t="n">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>90</v>
       </c>
       <c r="G22" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G23" t="n">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G24" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
         <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1242,7 +1242,7 @@
         <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D28" t="n">
         <v>10</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -3&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -522,7 +522,7 @@
         <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
         <v>16</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -582,7 +582,7 @@
         <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -612,7 +612,7 @@
         <v>87</v>
       </c>
       <c r="G6" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
@@ -642,7 +642,7 @@
         <v>102</v>
       </c>
       <c r="G7" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sergio_Fernandez</t>
+          <t>Raúl_Canabal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G8" t="n">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -686,23 +686,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Raúl_Canabal</t>
+          <t>Sergio_Fernandez</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G9" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
@@ -732,7 +732,7 @@
         <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -762,7 +762,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -776,23 +776,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -806,23 +806,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="n">
-        <v>11</v>
-      </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G13" t="n">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -836,23 +836,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alberto_Villardón</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G14" t="n">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -866,23 +866,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -896,23 +896,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Alberto_Villardón</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G16" t="n">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -926,23 +926,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -972,7 +972,7 @@
         <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -1002,7 +1002,7 @@
         <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -1032,7 +1032,7 @@
         <v>87</v>
       </c>
       <c r="G20" t="n">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1046,23 +1046,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G21" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1076,23 +1076,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G23" t="n">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
@@ -1152,7 +1152,7 @@
         <v>81</v>
       </c>
       <c r="G24" t="n">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
         <v>10</v>
@@ -1182,7 +1182,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1196,23 +1196,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G26" t="n">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1242,7 +1242,7 @@
         <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D28" t="n">
         <v>10</v>
@@ -1272,7 +1272,7 @@
         <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
         <v>16</v>
@@ -552,7 +552,7 @@
         <v>96</v>
       </c>
       <c r="G4" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
@@ -882,7 +882,7 @@
         <v>81</v>
       </c>
       <c r="G15" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
@@ -1242,7 +1242,7 @@
         <v>87</v>
       </c>
       <c r="G27" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -492,7 +492,7 @@
         <v>108</v>
       </c>
       <c r="G2" t="n">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -516,13 +516,13 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
         <v>93</v>
       </c>
       <c r="G3" t="n">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -536,27 +536,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos_Moreno</t>
+          <t>Álvaro_Vidal_Sánchez</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
         <v>16</v>
       </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
       <c r="F4" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G4" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -566,27 +566,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Álvaro_Vidal_Sánchez</t>
+          <t>Carlos_Moreno</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>David_Cabesa</t>
+          <t>Mario_Redondo_Carrasco</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
         <v>315</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -626,27 +626,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mario_Redondo_Carrasco</t>
+          <t>David_Cabesa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -672,7 +672,7 @@
         <v>96</v>
       </c>
       <c r="G8" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
@@ -702,7 +702,7 @@
         <v>99</v>
       </c>
       <c r="G9" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Nessi_Morant</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G11" t="n">
         <v>297</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nessi_Morant</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>43</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -912,7 +912,7 @@
         <v>81</v>
       </c>
       <c r="G16" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
@@ -942,7 +942,7 @@
         <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -1002,7 +1002,7 @@
         <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
         <v>268</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G21" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G22" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G23" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="n">
         <v>6</v>
       </c>
-      <c r="E24" t="n">
-        <v>7</v>
-      </c>
       <c r="F24" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G24" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G25" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G26" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>

--- a/clasificacion.xlsx
+++ b/clasificacion.xlsx
@@ -476,27 +476,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Noel_Olivares</t>
+          <t>David_De_Paz</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G2" t="n">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -506,27 +506,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David_De_Paz</t>
+          <t>Noel_Olivares</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvaro_Terron</t>
+          <t>Javier_Leton</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="G10" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -759,14 +759,14 @@
         <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G11" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Javier_Leton</t>
+          <t>Cristian_Luque</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G12" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jorge_Gamero</t>
+          <t>Alvaro_Terron</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
         <v>14</v>
       </c>
-      <c r="E13" t="n">
-        <v>8</v>
-      </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cristian_Luque</t>
+          <t>Alberto_Martin_Lopez</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="G14" t="n">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -866,27 +866,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alberto_Martin_Lopez</t>
+          <t>Jesús_García</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G15" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -909,14 +909,14 @@
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -926,27 +926,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jesús_García</t>
+          <t>Jorge_Gamero</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G17" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -969,10 +969,10 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G18" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Óscar_Espinosa</t>
+          <t>Javier_Sánchez_Moreno</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G20" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +2&lt;/span&gt;</t>
+          <t>&lt;span style='color:#00ff00'&gt;⬆️ +5&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1046,20 +1046,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ruth_Galvin</t>
+          <t>Óscar_Espinosa</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G21" t="n">
         <v>268</v>
@@ -1076,23 +1076,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Samuel_Fernández_Duarte</t>
+          <t>Ruth_Galvin</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1106,27 +1106,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Javier_Sánchez_Moreno</t>
+          <t>Javier_García</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G23" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Juan_Carlos_Ruiz</t>
+          <t>Samuel_Fernández_Duarte</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Javier_García</t>
+          <t>Ángel_Gutiérrez</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="G25" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#00ff00'&gt;⬆️ +1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -2&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ángel_Gutiérrez</t>
+          <t>Juan_Carlos_Ruiz</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D26" t="n">
         <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G26" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;span style='color:#ff4d4d'&gt;⬇️ -1&lt;/span&gt;</t>
+          <t>&lt;span style='color:#ffffff; font-weight:bold'&gt;=&lt;/span&gt;</t>
         </is>
       </c>
     </row>
@@ -1269,10 +1269,10 @@
         <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G28" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
